--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Fecha</t>
   </si>
@@ -36,13 +36,40 @@
     <t xml:space="preserve">Chiebuka Castro Ekwems</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementación de Viewport y Reescalado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperando la revisión y aprobación del Pull Request de Delta Time (afecta a todo el proyecto) para poder avanzar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alan Nicolás Valiente</t>
   </si>
   <si>
+    <t xml:space="preserve">Code Delta Time, Creación de Estados de Juego (Pausa y Game Over), e Implementación del HUD (Head-Up Display)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andrés Gorea</t>
   </si>
   <si>
+    <t xml:space="preserve">Migración a Delta Time (getDeltaTime)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creación de Pantalla de Inicio (Main Menu)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alexandre Soares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementación de Búnkeres Destructibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yago Martínez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soporte de Controles Multiplataforma (PC &amp; Mobile)</t>
   </si>
 </sst>
 </file>
@@ -52,12 +79,17 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.500000"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Liberation Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,15 +112,23 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E5">
-  <autoFilter ref="A1:E5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E6">
+  <autoFilter ref="A1:E6"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -603,58 +643,113 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="14.140625"/>
-    <col customWidth="1" min="2" max="2" width="23.7109375"/>
-    <col bestFit="1" min="3" max="3" width="15.22265625"/>
-    <col customWidth="1" min="4" max="4" width="16.8515625"/>
-    <col bestFit="1" min="5" max="5" width="15.80078125"/>
+    <col customWidth="1" min="2" max="2" style="1" width="23.7109375"/>
+    <col customWidth="1" min="3" max="3" style="2" width="25.57421875"/>
+    <col customWidth="1" min="4" max="4" style="2" width="33.28125"/>
+    <col customWidth="1" min="5" max="5" style="2" width="43.00390625"/>
+    <col min="6" max="6" style="1" width="9.140625"/>
+    <col min="7" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="14.25">
-      <c r="A2" s="2">
+    <row r="2" ht="42.75">
+      <c r="A2" s="3">
         <v>46155</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="2">
+    <row r="3" ht="57">
+      <c r="A3" s="3">
         <v>46155</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="2">
+    <row r="4" ht="42.75">
+      <c r="A4" s="3">
         <v>46155</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="2">
+    <row r="5" ht="42.75">
+      <c r="A5" s="3">
         <v>46155</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="42.75">
+      <c r="A6" s="3">
+        <v>46155</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Fecha</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Implementación de Viewport y Reescalado</t>
   </si>
   <si>
-    <t xml:space="preserve">Esperando la revisión y aprobación del Pull Request de Delta Time (afecta a todo el proyecto) para poder avanzar.</t>
+    <t xml:space="preserve">Esperando la revisión y aprobación PR delta time</t>
   </si>
   <si>
     <t xml:space="preserve">Alan Nicolás Valiente</t>
@@ -70,6 +70,27 @@
   </si>
   <si>
     <t xml:space="preserve">Soporte de Controles Multiplataforma (PC &amp; Mobile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema de Power-Ups (Drops y Efectos) y Revisión del PR División de funcionalidades controlador y Main </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobación PR delta time,Implementación del HUD (Head-Up Display), Revisión del PR División de funcionalidades controlador y Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementación del HUD Creación de Estados de Juego (Pausa y Game Over)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creación de Pantalla de Inicio (Main Menu) y División de funcionalidades controlador y Main </t>
+  </si>
+  <si>
+    <t xml:space="preserve">División de funcionalidades controlador y Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión del PR División de funcionalidades controlador y Main </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se le ha roto el pc, tiene que instalar configurar todo en otro</t>
   </si>
 </sst>
 </file>
@@ -147,8 +168,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E6">
-  <autoFilter ref="A1:E6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E11">
+  <autoFilter ref="A1:E11"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -644,11 +665,10 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="14.140625"/>
     <col customWidth="1" min="2" max="2" style="1" width="23.7109375"/>
-    <col customWidth="1" min="3" max="3" style="2" width="25.57421875"/>
+    <col customWidth="1" min="3" max="3" style="2" width="27.7109375"/>
     <col customWidth="1" min="4" max="4" style="2" width="33.28125"/>
     <col customWidth="1" min="5" max="5" style="2" width="43.00390625"/>
-    <col min="6" max="6" style="1" width="9.140625"/>
-    <col min="7" max="16384" style="1" width="9.140625"/>
+    <col min="6" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -698,7 +718,7 @@
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -709,7 +729,7 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -749,9 +769,129 @@
       <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="57">
+      <c r="A9" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75">
+      <c r="A11" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -91,6 +91,24 @@
   </si>
   <si>
     <t xml:space="preserve">Se le ha roto el pc, tiene que instalar configurar todo en otro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión Final del PR División de funcionalidades,  y corrección bug de balas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementación del HUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creación de Estados de Juego (Pausa y Game Over)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrección de la Revisión del PR División de funcionalidades y Creación de Pantalla de Inicio (Main Menu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menú de Opciones y Pantalla de Información</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema de Puntuación Variable y Vidas de Enemigos</t>
   </si>
 </sst>
 </file>
@@ -133,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +166,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -168,8 +189,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E11">
-  <autoFilter ref="A1:E11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E16">
+  <autoFilter ref="A1:E16"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -858,40 +879,90 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+    <row r="12" ht="42.75">
+      <c r="A12" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" ht="28.5">
+      <c r="A13" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" ht="57">
+      <c r="A14" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="A15" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" ht="28.5">
+      <c r="A16" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Fecha</t>
   </si>
@@ -109,6 +109,21 @@
   </si>
   <si>
     <t xml:space="preserve">Sistema de Puntuación Variable y Vidas de Enemigos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión final del PR 7</t>
+  </si>
+  <si>
+    <t>Pausa-GameOver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión, aprovación y resolución de conflictos PR 7 y 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar PR 10 y hacer Menú de Opciones y Pantalla de Información</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrección PR 8</t>
   </si>
 </sst>
 </file>
@@ -162,13 +177,13 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -189,8 +204,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E16">
-  <autoFilter ref="A1:E16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E21">
+  <autoFilter ref="A1:E21"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -709,7 +724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="42.75">
+    <row r="2" ht="28.5">
       <c r="A2" s="3">
         <v>46155</v>
       </c>
@@ -722,7 +737,7 @@
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -736,14 +751,14 @@
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="42.75">
+    <row r="4" ht="28.5">
       <c r="A4" s="3">
         <v>46155</v>
       </c>
@@ -760,7 +775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="42.75">
+    <row r="5" ht="28.5">
       <c r="A5" s="3">
         <v>46155</v>
       </c>
@@ -777,11 +792,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="42.75">
+    <row r="6" ht="28.5">
       <c r="A6" s="3">
         <v>46155</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -790,7 +805,7 @@
       <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -801,13 +816,13 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -818,13 +833,13 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -835,13 +850,13 @@
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -852,13 +867,13 @@
       <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -866,33 +881,33 @@
       <c r="A11" s="3">
         <v>46156</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" ht="42.75">
-      <c r="A12" s="6">
+      <c r="A12" s="3">
         <v>46157</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -903,13 +918,13 @@
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -920,10 +935,10 @@
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -937,13 +952,13 @@
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -951,7 +966,7 @@
       <c r="A16" s="3">
         <v>46157</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -960,7 +975,86 @@
       <c r="D16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5">
+      <c r="A19" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Fecha</t>
   </si>
@@ -124,6 +124,150 @@
   </si>
   <si>
     <t xml:space="preserve">Corrección PR 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión final del PR 7 y subida manual de assets faltantes.Discutió mantener el temporizador de cadencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementar la pantalla adaptable en develop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflictos de código con la rama de Yago.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminó lógica de Pausa y Game Over localmente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refactorizar al actualizar develop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolvió conflictos y cerró PR 7 y 8.Añadió bloque de disparo automático por la noche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar el PR 10 de Alan por la mañana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregidos comentarios del PR KAN-21 (cadencia, parada y botones Android).Eliminó autodisparo (contadorTiempoAmigo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reunión de equipo para resolver conflictos antes de KAN-27.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflictos entre PRs en GestorMundo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subió commit con la pantalla de Game Over y clase recursos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validar el correcto funcionamiento en develop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movió documentación a “reuniones” por orden del profesor.Explicó en IntelliJ cómo arreglar conflictos.Detectó y fusionó elementos faltantes en el PR de Alan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisar las ramas del equipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recibió orden de incluir su nombre en las ramas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retomar tareas asignadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ningún avance en el proyecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminar la cámara y elegir ticket en Jira.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistemas de persistencia de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retomar el trabajo al día siguiente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inició desarrollo del sistema de vidas de enemigos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminarlo por la noche tras el gimnasio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementó la pantalla adaptable (viewport) y abrió PR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperar aprobación del código.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retrasos por cita en el dentista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminar 3 tareas pendientes mañana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloqueado esperando la feature de Chiebuka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalizó su feature y pidió revisión al equipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizar llamada el sábado para resolver conflictos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demasiados elementos en la vista actual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminó KAN-27 (puntuación/vidas) y KAN-33 (Screen Shake/Hit Stop).Abrió PRs #13 y #15 apuntando a main por error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperar reviews para elegir nuevo ticket.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrolló e implementó la Nave Misteriosa (OVNI) y abrió PR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregar todo mañana y acabar música/sonidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detectó rama errónea de Yago que rompió recursos en develop.Aplicó un PR de “Fix” resolviendo 4 de 6 conflictos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probar la vibración táctil en Android.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pidió dailies atrasadas y mergeó el fix de Alan.Informó del backlog restante (audio, vibración, niveles, testeo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificar un modo infinito por rondas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmó que la vibración móvil ya estaba programada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar tickets pendientes en Jira desde el móvil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subió el .png faltante de la nave para arreglar el juego.Avanzó en el sistema de audio/música y abrió nuevo PR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitorear la revisión de su PR de sonido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avisó del fallo de compilación por falta del PNG del OVNI.Rediseñó los controles de Android añadiendo joystick y botón funcional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugerir niveles con dificultad progresiva y bosses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisó y mergeó el PR de la Nave Misteriosa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluar los nuevos cambios de audio dinámico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siguió el estado del proyecto desde el móvil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluar el desarrollo de niveles propuesto por Alan.</t>
   </si>
 </sst>
 </file>
@@ -141,7 +285,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.500000"/>
+      <sz val="11.000000"/>
       <color rgb="FF1F1F1F"/>
       <name val="Liberation Sans"/>
     </font>
@@ -166,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -182,9 +326,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -204,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla2" ref="A1:E21">
-  <autoFilter ref="A1:E21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="$A$1:$E$51">
+  <autoFilter ref="$A$1:$E$51"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -986,7 +1127,7 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="2"/>
@@ -998,10 +1139,10 @@
       <c r="A18" s="3">
         <v>46160</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="2"/>
@@ -1016,10 +1157,10 @@
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -1050,11 +1191,521 @@
       <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" ht="57">
+      <c r="A22" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="28.5">
+      <c r="A23" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" ht="42.75">
+      <c r="A24" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" ht="71.25">
+      <c r="A26" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" ht="28.5">
+      <c r="A28" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" ht="99.75">
+      <c r="A29" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" ht="28.5">
+      <c r="A31" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" ht="28.5">
+      <c r="A32" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" ht="28.5">
+      <c r="A33" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" ht="28.5">
+      <c r="A36" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" ht="42.75">
+      <c r="A37" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" ht="28.5">
+      <c r="A38" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" ht="28.5">
+      <c r="A39" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" ht="71.25">
+      <c r="A41" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" ht="42.75">
+      <c r="A42" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" ht="57">
+      <c r="A43" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" ht="57">
+      <c r="A44" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" ht="28.5">
+      <c r="A46" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" ht="57">
+      <c r="A47" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" ht="71.25">
+      <c r="A48" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" ht="28.5">
+      <c r="A49" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" ht="28.5">
+      <c r="A51" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>Fecha</t>
   </si>
@@ -268,6 +268,21 @@
   </si>
   <si>
     <t xml:space="preserve">Evaluar el desarrollo de niveles propuesto por Alan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nada este dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A estado fuera todo el dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix bugs, paralax escudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejorar escala del juego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asignacion y comienzo de implementación  Búnkeres Destructibles</t>
   </si>
 </sst>
 </file>
@@ -345,8 +360,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="$A$1:$E$51">
-  <autoFilter ref="$A$1:$E$51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E56">
+  <autoFilter ref="A1:E56"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -1257,13 +1272,13 @@
       <c r="B25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="C25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1291,13 +1306,13 @@
       <c r="B27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1342,13 +1357,13 @@
       <c r="B30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="C30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1393,13 +1408,13 @@
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1410,7 +1425,7 @@
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -1427,13 +1442,13 @@
       <c r="B35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="C35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1512,13 +1527,13 @@
       <c r="B40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="C40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1597,13 +1612,13 @@
       <c r="B45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="5" t="s">
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1682,13 +1697,13 @@
       <c r="B50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="5" t="s">
+      <c r="C50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1708,6 +1723,94 @@
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" ht="42.75">
+      <c r="A54" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="1"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Fecha</t>
   </si>
@@ -283,6 +283,21 @@
   </si>
   <si>
     <t xml:space="preserve">Asignacion y comienzo de implementación  Búnkeres Destructibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integración de Audio Dinámico (BGM y SFX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejorar la escala UI/UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión que mejoras implementar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix: Apartado de información (cierra el juego)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Añadir niveles</t>
   </si>
 </sst>
 </file>
@@ -360,8 +375,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E56">
-  <autoFilter ref="A1:E56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E61">
+  <autoFilter ref="A1:E61"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -1731,13 +1746,13 @@
       <c r="B52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="5" t="s">
+      <c r="D52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1748,13 +1763,13 @@
       <c r="B53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1765,7 +1780,7 @@
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -1806,11 +1821,96 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" ht="14.25">
-      <c r="A57" s="1"/>
+    <row r="57" ht="28.5">
+      <c r="A57" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="1"/>
+      <c r="A58" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" ht="28.5">
+      <c r="A59" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" ht="28.5">
+      <c r="A61" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Fecha</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t xml:space="preserve">Añadir niveles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar PR finalizadas</t>
   </si>
 </sst>
 </file>
@@ -375,8 +378,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E61">
-  <autoFilter ref="A1:E61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E66">
+  <autoFilter ref="A1:E66"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -1831,7 +1834,7 @@
       <c r="C57" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E57" s="2" t="s">
@@ -1845,7 +1848,7 @@
       <c r="B58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D58" s="2" t="s">
@@ -1865,7 +1868,7 @@
       <c r="C59" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E59" s="2" t="s">
@@ -1899,7 +1902,7 @@
       <c r="C61" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -1907,10 +1910,77 @@
       </c>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="1"/>
+      <c r="A62" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="1"/>
+      <c r="A63" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" ht="28.5">
+      <c r="A64" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="1"/>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>Fecha</t>
   </si>
@@ -301,6 +301,15 @@
   </si>
   <si>
     <t xml:space="preserve">Revisar PR finalizadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementación de niveles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejora escala UI-UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests unitarios</t>
   </si>
 </sst>
 </file>
@@ -378,8 +387,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E66">
-  <autoFilter ref="A1:E66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabla1" ref="A1:E71">
+  <autoFilter ref="A1:E71"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Persona"/>
@@ -1916,6 +1925,12 @@
       <c r="B62" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
       </c>
@@ -1927,6 +1942,12 @@
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
       </c>
@@ -1941,7 +1962,7 @@
       <c r="C64" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -1972,15 +1993,103 @@
       <c r="B66" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="C66" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="1"/>
+      <c r="A67" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="1"/>
+      <c r="A68" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="A72" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
